--- a/outputs/summary_report.xlsx
+++ b/outputs/summary_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-Month Forecast" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Model Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="6-Month Forecast" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/summary_report.xlsx
+++ b/outputs/summary_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Model Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="6-Month Forecast" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-Month Forecast" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6701</v>
+        <v>0.7517</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7385</v>
+        <v>0.8203</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2393</v>
+        <v>0.6019</v>
       </c>
     </row>
     <row r="3">
@@ -487,10 +487,10 @@
         <v>0.8639</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7506</v>
+        <v>0.8038</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2986</v>
+        <v>0.5052</v>
       </c>
     </row>
     <row r="4">
@@ -500,13 +500,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8673</v>
+        <v>0.8265</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7567</v>
+        <v>0.7869</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3234</v>
+        <v>0.4183</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/summary_report.xlsx
+++ b/outputs/summary_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Performance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-Month Forecast" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Model Performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="6-Month Forecast" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8639</v>
+        <v>0.8605</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8038</v>
+        <v>0.803</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5052</v>
+        <v>0.5049</v>
       </c>
     </row>
     <row r="4">
